--- a/セリフ編集/その他セリフ/10-通知ダイアログ.xlsx
+++ b/セリフ編集/その他セリフ/10-通知ダイアログ.xlsx
@@ -256,7 +256,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1._default.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -271,7 +271,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal._default[1]</t>
+          <t xml:space="preserve">N1._default.normal[1]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="5">
@@ -288,7 +288,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1._default.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -303,7 +303,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal._default[2]</t>
+          <t xml:space="preserve">N1._default.normal[2]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="5">
@@ -320,7 +320,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.bold._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1._default.bold[1]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.bold._default[1]</t>
+          <t xml:space="preserve">N1._default.bold[1]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="6">
@@ -352,7 +352,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.bold._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1._default.bold[2]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.bold._default[2]</t>
+          <t xml:space="preserve">N1._default.bold[2]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="6">
@@ -384,7 +384,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.quiet._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1._default.quiet[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.quiet._default[1]</t>
+          <t xml:space="preserve">N1._default.quiet[1]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="7">
@@ -416,7 +416,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.shy._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1._default.shy[1]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.shy._default[1]</t>
+          <t xml:space="preserve">N1._default.shy[1]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="8">
@@ -448,7 +448,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.easygoing._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.easygoing._default[1]</t>
+          <t xml:space="preserve">N1._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="9">
@@ -480,7 +480,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.easygoing._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.easygoing._default[2]</t>
+          <t xml:space="preserve">N1._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="9">
@@ -512,7 +512,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1._default.earnest[1]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.earnest._default[1]</t>
+          <t xml:space="preserve">N1._default.earnest[1]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="10">
@@ -544,7 +544,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1._default.earnest[2]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.earnest._default[2]</t>
+          <t xml:space="preserve">N1._default.earnest[2]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="10">
@@ -576,7 +576,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.emotional._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1._default.emotional[1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.emotional._default[1]</t>
+          <t xml:space="preserve">N1._default.emotional[1]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="10">
@@ -608,7 +608,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.emotional._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1._default.emotional[2]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.emotional._default[2]</t>
+          <t xml:space="preserve">N1._default.emotional[2]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="10">
@@ -640,7 +640,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2._default.normal[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.normal._default[1]</t>
+          <t xml:space="preserve">N2._default.normal[1]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="5">
@@ -672,7 +672,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2._default.normal[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.normal._default[2]</t>
+          <t xml:space="preserve">N2._default.normal[2]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="5">
@@ -704,7 +704,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.bold._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2._default.bold[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.bold._default[1]</t>
+          <t xml:space="preserve">N2._default.bold[1]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="6">
@@ -736,7 +736,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.bold._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2._default.bold[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.bold._default[2]</t>
+          <t xml:space="preserve">N2._default.bold[2]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="6">
@@ -768,7 +768,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.quiet._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2._default.quiet[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.quiet._default[1]</t>
+          <t xml:space="preserve">N2._default.quiet[1]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="7">
@@ -800,7 +800,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.shy._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2._default.shy[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.shy._default[1]</t>
+          <t xml:space="preserve">N2._default.shy[1]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="8">
@@ -832,7 +832,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.easygoing._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.easygoing._default[1]</t>
+          <t xml:space="preserve">N2._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="9">
@@ -864,7 +864,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2._default.earnest[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.earnest._default[1]</t>
+          <t xml:space="preserve">N2._default.earnest[1]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="10">
@@ -896,7 +896,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2._default.earnest[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.earnest._default[2]</t>
+          <t xml:space="preserve">N2._default.earnest[2]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="10">
@@ -928,7 +928,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.emotional._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2._default.emotional[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.emotional._default[1]</t>
+          <t xml:space="preserve">N2._default.emotional[1]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="10">
@@ -960,7 +960,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3._default.normal[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.normal._default[1]</t>
+          <t xml:space="preserve">N3._default.normal[1]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="5">
@@ -992,7 +992,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3._default.normal[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.normal._default[2]</t>
+          <t xml:space="preserve">N3._default.normal[2]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="5">
@@ -1024,7 +1024,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.bold._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3._default.bold[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.bold._default[1]</t>
+          <t xml:space="preserve">N3._default.bold[1]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="6">
@@ -1056,7 +1056,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.bold._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3._default.bold[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.bold._default[2]</t>
+          <t xml:space="preserve">N3._default.bold[2]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="6">
@@ -1088,7 +1088,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.quiet._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3._default.quiet[1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.quiet._default[1]</t>
+          <t xml:space="preserve">N3._default.quiet[1]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="7">
@@ -1120,7 +1120,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.shy._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3._default.shy[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.shy._default[1]</t>
+          <t xml:space="preserve">N3._default.shy[1]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="8">
@@ -1152,7 +1152,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.easygoing._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.easygoing._default[1]</t>
+          <t xml:space="preserve">N3._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="9">
@@ -1184,7 +1184,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3._default.earnest[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.earnest._default[1]</t>
+          <t xml:space="preserve">N3._default.earnest[1]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="10">
@@ -1216,7 +1216,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3._default.earnest[2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.earnest._default[2]</t>
+          <t xml:space="preserve">N3._default.earnest[2]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="10">
@@ -1248,7 +1248,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.emotional._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3._default.emotional[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.emotional._default[1]</t>
+          <t xml:space="preserve">N3._default.emotional[1]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="10">
@@ -1280,7 +1280,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4._default.normal[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.normal._default[1]</t>
+          <t xml:space="preserve">N4._default.normal[1]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="5">
@@ -1312,7 +1312,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4._default.normal[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.normal._default[2]</t>
+          <t xml:space="preserve">N4._default.normal[2]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="5">
@@ -1344,7 +1344,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.bold._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4._default.bold[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.bold._default[1]</t>
+          <t xml:space="preserve">N4._default.bold[1]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="6">
@@ -1376,7 +1376,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.bold._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4._default.bold[2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.bold._default[2]</t>
+          <t xml:space="preserve">N4._default.bold[2]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="6">
@@ -1408,7 +1408,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.quiet._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4._default.quiet[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.quiet._default[1]</t>
+          <t xml:space="preserve">N4._default.quiet[1]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="7">
@@ -1440,7 +1440,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.shy._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4._default.shy[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.shy._default[1]</t>
+          <t xml:space="preserve">N4._default.shy[1]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="8">
@@ -1472,7 +1472,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.easygoing._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.easygoing._default[1]</t>
+          <t xml:space="preserve">N4._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="9">
@@ -1504,7 +1504,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.easygoing._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.easygoing._default[2]</t>
+          <t xml:space="preserve">N4._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="9">
@@ -1536,7 +1536,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4._default.earnest[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.earnest._default[1]</t>
+          <t xml:space="preserve">N4._default.earnest[1]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="10">
@@ -1568,7 +1568,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4._default.earnest[2]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.earnest._default[2]</t>
+          <t xml:space="preserve">N4._default.earnest[2]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="10">
@@ -1600,7 +1600,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.emotional._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4._default.emotional[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.emotional._default[1]</t>
+          <t xml:space="preserve">N4._default.emotional[1]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="10">
@@ -1632,7 +1632,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning._default.normal[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.normal._default[1]</t>
+          <t xml:space="preserve">N5_warning._default.normal[1]</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="5">
@@ -1664,7 +1664,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning._default.normal[2]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.normal._default[2]</t>
+          <t xml:space="preserve">N5_warning._default.normal[2]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="5">
@@ -1696,7 +1696,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.bold._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning._default.bold[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.bold._default[1]</t>
+          <t xml:space="preserve">N5_warning._default.bold[1]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="6">
@@ -1728,7 +1728,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.bold._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning._default.bold[2]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.bold._default[2]</t>
+          <t xml:space="preserve">N5_warning._default.bold[2]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="6">
@@ -1760,7 +1760,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.shy._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning._default.shy[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.shy._default[1]</t>
+          <t xml:space="preserve">N5_warning._default.shy[1]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="8">
@@ -1792,7 +1792,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.easygoing._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.easygoing._default[1]</t>
+          <t xml:space="preserve">N5_warning._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="9">
@@ -1824,7 +1824,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning._default.earnest[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.earnest._default[1]</t>
+          <t xml:space="preserve">N5_warning._default.earnest[1]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="10">
@@ -1856,7 +1856,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning._default.earnest[2]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.earnest._default[2]</t>
+          <t xml:space="preserve">N5_warning._default.earnest[2]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="10">
@@ -1888,7 +1888,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.emotional._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning._default.emotional[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.emotional._default[1]</t>
+          <t xml:space="preserve">N5_warning._default.emotional[1]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="10">
@@ -1920,7 +1920,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low._default.normal[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.normal._default[1]</t>
+          <t xml:space="preserve">N5_low._default.normal[1]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="5">
@@ -1952,7 +1952,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low._default.normal[2]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.normal._default[2]</t>
+          <t xml:space="preserve">N5_low._default.normal[2]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="5">
@@ -1984,7 +1984,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.bold._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low._default.bold[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.bold._default[1]</t>
+          <t xml:space="preserve">N5_low._default.bold[1]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="6">
@@ -2016,7 +2016,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.bold._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low._default.bold[2]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.bold._default[2]</t>
+          <t xml:space="preserve">N5_low._default.bold[2]</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="6">
@@ -2048,7 +2048,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.quiet._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low._default.quiet[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.quiet._default[1]</t>
+          <t xml:space="preserve">N5_low._default.quiet[1]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="7">
@@ -2080,7 +2080,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.shy._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low._default.shy[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.shy._default[1]</t>
+          <t xml:space="preserve">N5_low._default.shy[1]</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="8">
@@ -2112,7 +2112,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.easygoing._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.easygoing._default[1]</t>
+          <t xml:space="preserve">N5_low._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="9">
@@ -2144,7 +2144,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low._default.earnest[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.earnest._default[1]</t>
+          <t xml:space="preserve">N5_low._default.earnest[1]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="10">
@@ -2176,7 +2176,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest._default[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low._default.earnest[2]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.earnest._default[2]</t>
+          <t xml:space="preserve">N5_low._default.earnest[2]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="10">
@@ -2208,7 +2208,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.emotional._default[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low._default.emotional[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.emotional._default[1]</t>
+          <t xml:space="preserve">N5_low._default.emotional[1]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="10">
